--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127474222</v>
       </c>
       <c r="B2" t="n">
-        <v>106038</v>
+        <v>106044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127474405</v>
       </c>
       <c r="B3" t="n">
-        <v>75145</v>
+        <v>75149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127474222</v>
       </c>
       <c r="B2" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127474222</v>
       </c>
       <c r="B2" t="n">
-        <v>106046</v>
+        <v>106048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127474405</v>
       </c>
       <c r="B3" t="n">
-        <v>75149</v>
+        <v>75151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127474222</v>
       </c>
       <c r="B2" t="n">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127474222</v>
       </c>
       <c r="B2" t="n">
-        <v>106054</v>
+        <v>106057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127474405</v>
       </c>
       <c r="B3" t="n">
-        <v>75151</v>
+        <v>75154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127474222</v>
       </c>
       <c r="B2" t="n">
-        <v>106057</v>
+        <v>106065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127474405</v>
       </c>
       <c r="B3" t="n">
-        <v>75154</v>
+        <v>75160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127474222</v>
       </c>
       <c r="B2" t="n">
-        <v>106065</v>
+        <v>106066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127474222</v>
       </c>
       <c r="B2" t="n">
-        <v>106066</v>
+        <v>106067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127474222</v>
       </c>
       <c r="B2" t="n">
-        <v>106067</v>
+        <v>106068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127474222</v>
+        <v>57070806</v>
       </c>
       <c r="B2" t="n">
-        <v>106068</v>
+        <v>83315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>1469</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tubbaremma, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459333</v>
+        <v>459309</v>
       </c>
       <c r="R2" t="n">
-        <v>6294689</v>
+        <v>6294699</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2016-02-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Jättetråd, omkrets 528 cm. Döende. Gulvit blekspik 2dm2.</t>
+          <t>2016-02-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,16 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>jätteask</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Mortlock</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Caroline Mortlock, Per Darell</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -784,7 +795,7 @@
         <v>127474405</v>
       </c>
       <c r="B3" t="n">
-        <v>75160</v>
+        <v>83314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,6 +902,306 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129109041</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tubbamåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>459316</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6294699</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vislanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ida Odenius</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ida Odenius</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127474222</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tubbaremma, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>459333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6294689</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vislanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Jättetråd, omkrets 528 cm. Döende. Gulvit blekspik 2dm2.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129109052</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tubbamåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>459316</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6294700</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vislanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ida Odenius</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ida Odenius</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18207-2023 artfynd.xlsx
+++ b/artfynd/A 18207-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57070806</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127474405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129109041</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127474222</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129109052</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>